--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="292">
   <si>
     <t>Property</t>
   </si>
@@ -483,9 +483,6 @@
     <t>statusプロパティは、operationStatus、またはロケーションに構成されている場合はスケジュール/スロットによってカバーされる可能性がある現在の値ではなく、リソースの一般的な可用性をカバーする。</t>
   </si>
   <si>
-    <t>FHIR文字列はサイズが1MBを超えてはならないことに注意すること</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -863,9 +860,6 @@
   </si>
   <si>
     <t>開始時刻と終了時刻の間に利用可能な曜日を示す。</t>
-  </si>
-  <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意すること。</t>
   </si>
   <si>
     <t>曜日</t>
@@ -2502,9 +2496,7 @@
       <c r="M12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2529,13 +2521,13 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2568,18 +2560,18 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2602,16 +2594,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2640,11 +2632,11 @@
         <v>109</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
       </c>
@@ -2661,7 +2653,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2676,18 +2668,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2710,16 +2702,16 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2769,7 +2761,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2784,7 +2776,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
@@ -2792,10 +2784,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2818,19 +2810,19 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2879,7 +2871,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2894,7 +2886,7 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -2902,10 +2894,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2928,19 +2920,17 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" s="2"/>
+      <c r="O16" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2989,7 +2979,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3004,7 +2994,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3012,10 +3002,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3041,16 +3031,16 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3075,14 +3065,14 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
       </c>
@@ -3099,7 +3089,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3114,18 +3104,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3148,16 +3138,16 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3183,14 +3173,14 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
       </c>
@@ -3207,7 +3197,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3222,18 +3212,18 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3256,13 +3246,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3313,7 +3303,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3328,7 +3318,7 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3336,10 +3326,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3362,19 +3352,19 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3423,7 +3413,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3438,7 +3428,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -3446,10 +3436,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3472,19 +3462,19 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3509,14 +3499,14 @@
         <v>76</v>
       </c>
       <c r="X21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Y21" t="s" s="2">
+      <c r="Z21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>217</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>76</v>
       </c>
@@ -3533,7 +3523,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3548,18 +3538,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3582,17 +3572,17 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3641,7 +3631,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3656,7 +3646,7 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -3664,10 +3654,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3690,13 +3680,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3747,7 +3737,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3762,7 +3752,7 @@
         <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
@@ -3770,10 +3760,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3802,7 +3792,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3855,7 +3845,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3870,7 +3860,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -3878,14 +3868,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3907,10 +3897,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3965,7 +3955,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3988,10 +3978,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4014,16 +4004,16 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4073,7 +4063,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>85</v>
@@ -4088,7 +4078,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4096,10 +4086,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4122,16 +4112,16 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4181,7 +4171,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -4196,7 +4186,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4204,10 +4194,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4230,16 +4220,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4289,7 +4279,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4304,7 +4294,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4312,10 +4302,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4338,19 +4328,19 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4399,7 +4389,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4414,7 +4404,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4422,10 +4412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4448,19 +4438,19 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4509,7 +4499,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4524,7 +4514,7 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -4532,10 +4522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4558,16 +4548,16 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4617,7 +4607,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4632,7 +4622,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -4640,10 +4630,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4666,13 +4656,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4723,7 +4713,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4738,7 +4728,7 @@
         <v>76</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -4746,10 +4736,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4778,7 +4768,7 @@
         <v>132</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>134</v>
@@ -4831,7 +4821,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4846,7 +4836,7 @@
         <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -4854,14 +4844,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4883,10 +4873,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>134</v>
@@ -4941,7 +4931,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -4964,10 +4954,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4993,14 +4983,12 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>274</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5025,13 +5013,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5049,7 +5037,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5064,7 +5052,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5072,10 +5060,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5098,13 +5086,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5155,7 +5143,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5170,7 +5158,7 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5178,10 +5166,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5204,13 +5192,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5261,7 +5249,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5276,7 +5264,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5284,10 +5272,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5310,13 +5298,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5367,7 +5355,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5382,7 +5370,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5390,10 +5378,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5416,13 +5404,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5473,7 +5461,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5488,7 +5476,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -5496,10 +5484,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5522,19 +5510,19 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -5583,7 +5571,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5598,7 +5586,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
